--- a/Data/LREROBOT/Variables.xlsx
+++ b/Data/LREROBOT/Variables.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
-  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <x:workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\LREROBOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE\Data\LREROBOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7084D900-C50B-477E-BD2F-3B6F5B1935CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="22245" firstSheet="0" activeTab="0"/>
+    <x:workbookView xWindow="9360" yWindow="4350" windowWidth="38700" windowHeight="15225" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Variables" sheetId="3" r:id="rId1"/>
@@ -34,19 +35,67 @@
     <x:t>Value</x:t>
   </x:si>
   <x:si>
+    <x:t>Date</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08/08/2025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>idLot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>idDocument</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
     <x:t>Heure de début</x:t>
   </x:si>
   <x:si>
-    <x:t>15:43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Date</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06/08/2025</x:t>
-  </x:si>
-  <x:si>
-    <x:t>idLot</x:t>
+    <x:t>00:13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PDF OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>135</x:t>
+  </x:si>
+  <x:si>
+    <x:t>total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>224</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REJET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hors Perimetre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Heure de Fin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00:15</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -55,7 +104,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
@@ -375,7 +424,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -402,6 +451,86 @@
         <x:v>3</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" spans="1:2">
+      <x:c r="A3" s="0" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:2">
+      <x:c r="A4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:2">
+      <x:c r="A5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:2">
+      <x:c r="A6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:2">
+      <x:c r="A7" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:2">
+      <x:c r="A8" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:2">
+      <x:c r="A9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:2">
+      <x:c r="A10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:2">
+      <x:c r="A11" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:2">
+      <x:c r="A12" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -412,11 +541,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0100-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B3"/>
+  <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
     <x:col min="1" max="1" width="6.285156" style="0" bestFit="1" customWidth="1"/>
@@ -431,20 +560,20 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <x:row r="2" spans="1:3">
       <x:c r="A2" s="0" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3">
+      <x:c r="A3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <x:c r="A3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/LREROBOT/Variables.xlsx
+++ b/Data/LREROBOT/Variables.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <x:fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
-  <x:workbookPr codeName="ThisWorkbook"/>
+<x:workbook xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x15">
+  <x:fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <x:workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walid ABRA\Documents\UiPath\PerformerProjet1LRE\Data\LREROBOT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpa.lre.res.dev\Documents\UiPath\PerformerProjet1LRE\Data\LREROBOT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7084D900-C50B-477E-BD2F-3B6F5B1935CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <x:bookViews>
-    <x:workbookView xWindow="9360" yWindow="4350" windowWidth="38700" windowHeight="15225" firstSheet="0" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <x:workbookView xWindow="9360" yWindow="4350" windowWidth="38700" windowHeight="15225" firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="Variables" sheetId="3" r:id="rId1"/>
@@ -35,76 +34,58 @@
     <x:t>Value</x:t>
   </x:si>
   <x:si>
+    <x:t>Heure de début</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14:42</x:t>
+  </x:si>
+  <x:si>
+    <x:t>idDocument</x:t>
+  </x:si>
+  <x:si>
+    <x:t>152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B</x:t>
+  </x:si>
+  <x:si>
+    <x:t>159</x:t>
+  </x:si>
+  <x:si>
+    <x:t>REJET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hors Perimetre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Heure de Fin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14:44</x:t>
+  </x:si>
+  <x:si>
     <x:t>Date</x:t>
   </x:si>
   <x:si>
-    <x:t>08/08/2025</x:t>
+    <x:t>13/08/2025</x:t>
   </x:si>
   <x:si>
     <x:t>idLot</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>idDocument</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Heure de début</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00:13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PDF OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>135</x:t>
-  </x:si>
-  <x:si>
-    <x:t>total</x:t>
-  </x:si>
-  <x:si>
-    <x:t>224</x:t>
-  </x:si>
-  <x:si>
-    <x:t>B</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82</x:t>
-  </x:si>
-  <x:si>
-    <x:t>REJET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>89</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hors Perimetre</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ZIP</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Heure de Fin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00:15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2 xr">
+<x:styleSheet xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac x16r2">
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
@@ -424,7 +405,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0000-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -472,63 +453,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:2">
-      <x:c r="A9" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B9" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:2">
-      <x:c r="A10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:2">
-      <x:c r="A11" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:2">
-      <x:c r="A12" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -541,11 +490,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xr:uid="{00000000-0001-0000-0100-000000000000}" mc:Ignorable="x14ac xr xr2 xr3">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B1"/>
+  <x:dimension ref="A1:B3"/>
   <x:sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <x:cols>
     <x:col min="1" max="1" width="6.285156" style="0" bestFit="1" customWidth="1"/>
@@ -560,20 +509,20 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:3">
+    <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/LREROBOT/Variables.xlsx
+++ b/Data/LREROBOT/Variables.xlsx
@@ -37,49 +37,67 @@
     <x:t>Heure de début</x:t>
   </x:si>
   <x:si>
-    <x:t>14:42</x:t>
+    <x:t>11:56</x:t>
   </x:si>
   <x:si>
     <x:t>idDocument</x:t>
   </x:si>
   <x:si>
-    <x:t>152</x:t>
+    <x:t>0</x:t>
   </x:si>
   <x:si>
     <x:t>B</x:t>
   </x:si>
   <x:si>
-    <x:t>159</x:t>
+    <x:t>32</x:t>
   </x:si>
   <x:si>
     <x:t>REJET</x:t>
   </x:si>
   <x:si>
+    <x:t>33</x:t>
+  </x:si>
+  <x:si>
     <x:t>total</x:t>
   </x:si>
   <x:si>
+    <x:t>172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PDF OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>139</x:t>
+  </x:si>
+  <x:si>
     <x:t>Hors Perimetre</x:t>
   </x:si>
   <x:si>
-    <x:t>61</x:t>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZIP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
   </x:si>
   <x:si>
     <x:t>Heure de Fin</x:t>
   </x:si>
   <x:si>
-    <x:t>14:44</x:t>
+    <x:t>11:59</x:t>
   </x:si>
   <x:si>
     <x:t>Date</x:t>
   </x:si>
   <x:si>
-    <x:t>13/08/2025</x:t>
+    <x:t>29/08/2025</x:t>
   </x:si>
   <x:si>
     <x:t>idLot</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
+    <x:t>4</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -453,31 +471,47 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:2">
+      <x:c r="A9" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:2">
+      <x:c r="A10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -511,18 +545,18 @@
     </x:row>
     <x:row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A2" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <x:c r="A3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
